--- a/scripts/tests/fixtures/evolution/workbook-200900002-quarter.xlsx
+++ b/scripts/tests/fixtures/evolution/workbook-200900002-quarter.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="111">
   <si>
     <t>{{report.title}}</t>
   </si>
@@ -79,7 +79,7 @@
     <t>Deposits</t>
   </si>
   <si>
-    <t>Withdrawals *</t>
+    <t>Withdrawals{{footnote.periods.withdrawals}}</t>
   </si>
   <si>
     <t>Net flows</t>
@@ -103,99 +103,114 @@
     <t>Realized on sales</t>
   </si>
   <si>
-    <t>Income *</t>
+    <t>Income{{footnote.periods.income}}</t>
   </si>
   <si>
     <t>Realized total</t>
   </si>
   <si>
-    <t>Fees *</t>
+    <t>Fees{{footnote.periods.fees}}</t>
+  </si>
+  <si>
+    <t>FX costs{{footnote.periods.fx_costs}}</t>
+  </si>
+  <si>
+    <t>Costs total</t>
+  </si>
+  <si>
+    <t>Cash movements</t>
+  </si>
+  <si>
+    <t>FX on cash</t>
+  </si>
+  <si>
+    <t>Unexplained</t>
+  </si>
+  <si>
+    <t>Priced</t>
+  </si>
+  <si>
+    <t>Unpriced</t>
+  </si>
+  <si>
+    <t>No rate</t>
+  </si>
+  <si>
+    <t>Missing rate</t>
+  </si>
+  <si>
+    <t>{{table:periods|period,period_start,period_end,portfolio_id,currency,invested_open,market_value_open,cash_open,unrealized_open,fx_unrealized_open,deposits,withdrawals,flows_net,purchases_at_cost,transfers_in_at_cost,sales_at_cost,transfers_out_at_cost,sales_proceeds,realized_sales,fx_realized,income,realized_total,fees,fx_costs,costs_total,cash_movements,fx_cash,invested_close,market_value_close,cash_close,unrealized_close,fx_unrealized_close,unexplained,priced_instruments,unpriced_instruments,unconverted,missing_rate}}</t>
+  </si>
+  <si>
+    <t>{{table:periods_notes|note}}</t>
+  </si>
+  <si>
+    <t>Net contributions</t>
+  </si>
+  <si>
+    <t>Income{{footnote.summary.income_total}}</t>
+  </si>
+  <si>
+    <t>Costs total{{footnote.summary.costs_total}}</t>
+  </si>
+  <si>
+    <t>Unrealized, start</t>
+  </si>
+  <si>
+    <t>Unrealized, end</t>
+  </si>
+  <si>
+    <t>Performance</t>
+  </si>
+  <si>
+    <t>Plain return %</t>
+  </si>
+  <si>
+    <t>{{table:summary|portfolio_id,currency,net_contributions,realized_sales_total,fx_realized_total,income_total,realized_total,costs_total,fx_cash_total,unrealized_start,unrealized_end,fx_unrealized_end,performance,plain_return_pct}}</t>
+  </si>
+  <si>
+    <t>{{table:summary_notes|note}}</t>
+  </si>
+  <si>
+    <t>Invested at cost and market value, period by period</t>
+  </si>
+  <si>
+    <t>{{table:summary_series|portfolio_id,period,period_end,currency,invested_close,market_value_close}}</t>
+  </si>
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>{{table:notes_facts|item,value}}</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>{{table:notes_facts_notes|note}}</t>
+  </si>
+  <si>
+    <t>Investment evolution — Fixture dollar (conseq:200900002)</t>
+  </si>
+  <si>
+    <t>2025-07-01 – 2026-06-15 · by quarter · in USD · average cost</t>
+  </si>
+  <si>
+    <t>Withdrawals</t>
+  </si>
+  <si>
+    <t>Income</t>
+  </si>
+  <si>
+    <t>Fees</t>
   </si>
   <si>
     <t>FX costs *</t>
   </si>
   <si>
-    <t>Costs total</t>
-  </si>
-  <si>
-    <t>Cash movements</t>
-  </si>
-  <si>
-    <t>FX on cash</t>
-  </si>
-  <si>
-    <t>Unexplained</t>
-  </si>
-  <si>
-    <t>Priced</t>
-  </si>
-  <si>
-    <t>Unpriced</t>
-  </si>
-  <si>
-    <t>No rate</t>
-  </si>
-  <si>
-    <t>Missing rate</t>
-  </si>
-  <si>
-    <t>{{table:periods|period,period_start,period_end,portfolio_id,currency,invested_open,market_value_open,cash_open,unrealized_open,fx_unrealized_open,deposits,withdrawals,flows_net,purchases_at_cost,transfers_in_at_cost,sales_at_cost,transfers_out_at_cost,sales_proceeds,realized_sales,fx_realized,income,realized_total,fees,fx_costs,costs_total,cash_movements,fx_cash,invested_close,market_value_close,cash_close,unrealized_close,fx_unrealized_close,unexplained,priced_instruments,unpriced_instruments,unconverted,missing_rate}}</t>
-  </si>
-  <si>
-    <t>{{table:periods_notes|note}}</t>
-  </si>
-  <si>
-    <t>Net contributions</t>
-  </si>
-  <si>
-    <t>Costs total *</t>
-  </si>
-  <si>
-    <t>Unrealized, start</t>
-  </si>
-  <si>
-    <t>Unrealized, end</t>
-  </si>
-  <si>
-    <t>Performance</t>
-  </si>
-  <si>
-    <t>Plain return %</t>
-  </si>
-  <si>
-    <t>{{table:summary|portfolio_id,currency,net_contributions,realized_sales_total,fx_realized_total,income_total,realized_total,costs_total,fx_cash_total,unrealized_start,unrealized_end,fx_unrealized_end,performance,plain_return_pct}}</t>
-  </si>
-  <si>
-    <t>{{table:summary_notes|note}}</t>
-  </si>
-  <si>
-    <t>Invested at cost and market value, period by period</t>
-  </si>
-  <si>
-    <t>{{table:summary_series|portfolio_id,period,period_end,currency,invested_close,market_value_close}}</t>
-  </si>
-  <si>
-    <t>Item</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>{{table:notes_facts|item,value}}</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>{{table:notes_facts_notes|note}}</t>
-  </si>
-  <si>
-    <t>Investment evolution — Fixture dollar (conseq:200900002)</t>
-  </si>
-  <si>
-    <t>2025-07-01 – 2026-06-15 · by quarter · in USD · average cost</t>
-  </si>
-  <si>
     <t>2025-Q3</t>
   </si>
   <si>
@@ -220,10 +235,10 @@
     <t>2026-Q2</t>
   </si>
   <si>
-    <t>* withdrawals — Conseq books an entry fee as a withdrawal beside its deposit; it stays inside withdrawals until the model carries each movement's description (IA-C49, IA-P4b).</t>
-  </si>
-  <si>
-    <t>* income, fees, fx_costs — 0: the model carries no fee and no description to tell them by, and none is inferred from an amount (IA-C49, IA-P4b).</t>
+    <t>withdrawals, fees, income — by the provider's label of each movement (income-labels.yaml, named on the Notes): Conseq's entry fees and commissions leave withdrawals for fees; income is what the table classes dividend, coupon or interest. A cash-leg fee or income is shown there too and stays in cash_movements — once: when the external-flow leg carries the same payment (a cash-account contract books a fee on both), the flow counts it.</t>
+  </si>
+  <si>
+    <t>* fx_costs — 0: the model carries no conversion fee, and none is inferred from an amount (IA-C49).</t>
   </si>
   <si>
     <t>fx_unrealized_open, fx_realized and fx_unrealized_close are the exchange-rate parts of the figures beside them — shown, never added to them.</t>
@@ -286,7 +301,7 @@
     <t>Income and fees</t>
   </si>
   <si>
-    <t>not available: the model carries no `fee`/`description`; fees, income and entry fees read 0, and entry fees stay inside withdrawals (IA-C49)</t>
+    <t>classified by income-labels.yaml v1 (14 labels); 1 of 2 cash and external-flow movements carry a label the table does not know, counted as other ('výplata na účet xy' ×1); 0 carry no label</t>
   </si>
   <si>
     <t>Exchange rates</t>
@@ -316,7 +331,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-15T08:00:00Z</t>
+    <t>2026-10-04T19:00:42Z</t>
   </si>
   <si>
     <t>As of 2026-06-15, by quarter; prices are the latest on or before each period end.</t>
@@ -325,7 +340,7 @@
     <t>Cost basis: average (REPORT_COST_BASIS).</t>
   </si>
   <si>
-    <t>Income and fees: not available: the model carries no `fee`/`description`; fees, income and entry fees read 0, and entry fees stay inside withdrawals (IA-C49).</t>
+    <t>Income and fees: classified by income-labels.yaml v1 (14 labels); 1 of 2 cash and external-flow movements carry a label the table does not know, counted as other ('výplata na účet xy' ×1); 0 carry no label.</t>
   </si>
   <si>
     <t>Amounts are in USD, each converted at its own day's rate from investment.fx_rate (the ČNB fixing via cnb-rates, IA-C68) — the latest rate on or before that day; an amount with no rate is never converted at a guess.</t>
@@ -464,12 +479,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="4">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4">
@@ -564,7 +579,7 @@
         <v>20</v>
       </c>
       <c r="L5" t="s" s="6">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="M5" t="s" s="6">
         <v>22</v>
@@ -591,16 +606,16 @@
         <v>19</v>
       </c>
       <c r="U5" t="s" s="6">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="V5" t="s" s="6">
         <v>30</v>
       </c>
       <c r="W5" t="s" s="6">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="X5" t="s" s="6">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="Y5" t="s" s="6">
         <v>33</v>
@@ -644,7 +659,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B6" s="8" t="n">
         <v>45839.0</v>
@@ -653,10 +668,10 @@
         <v>45930.0</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F6" s="9" t="n">
         <v>0.0</v>
@@ -752,12 +767,12 @@
         <v>0.0</v>
       </c>
       <c r="AK6" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B7" s="8" t="n">
         <v>45839.0</v>
@@ -766,10 +781,10 @@
         <v>45930.0</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>0.0</v>
@@ -865,12 +880,12 @@
         <v>0.0</v>
       </c>
       <c r="AK7" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B8" s="8" t="n">
         <v>45931.0</v>
@@ -879,10 +894,10 @@
         <v>46022.0</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>560.0</v>
@@ -978,12 +993,12 @@
         <v>0.0</v>
       </c>
       <c r="AK8" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B9" s="8" t="n">
         <v>45931.0</v>
@@ -992,10 +1007,10 @@
         <v>46022.0</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F9" s="9" t="n">
         <v>560.0</v>
@@ -1091,12 +1106,12 @@
         <v>0.0</v>
       </c>
       <c r="AK9" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B10" s="8" t="n">
         <v>46023.0</v>
@@ -1105,10 +1120,10 @@
         <v>46112.0</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>560.0</v>
@@ -1204,12 +1219,12 @@
         <v>0.0</v>
       </c>
       <c r="AK10" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B11" s="8" t="n">
         <v>46023.0</v>
@@ -1218,10 +1233,10 @@
         <v>46112.0</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F11" s="9" t="n">
         <v>560.0</v>
@@ -1317,12 +1332,12 @@
         <v>0.0</v>
       </c>
       <c r="AK11" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B12" s="8" t="n">
         <v>46113.0</v>
@@ -1331,10 +1346,10 @@
         <v>46188.0</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F12" s="9" t="n">
         <v>336.0</v>
@@ -1430,12 +1445,12 @@
         <v>0.0</v>
       </c>
       <c r="AK12" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B13" s="8" t="n">
         <v>46113.0</v>
@@ -1444,10 +1459,10 @@
         <v>46188.0</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F13" s="9" t="n">
         <v>336.0</v>
@@ -1543,32 +1558,32 @@
         <v>0.0</v>
       </c>
       <c r="AK13" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -1599,12 +1614,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="4">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4">
@@ -1624,39 +1639,39 @@
         <v>19</v>
       </c>
       <c r="F4" t="s" s="6">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="G4" t="s" s="6">
         <v>30</v>
       </c>
       <c r="H4" t="s" s="6">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="I4" t="s" s="6">
         <v>35</v>
       </c>
       <c r="J4" t="s" s="6">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K4" t="s" s="6">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L4" t="s" s="6">
         <v>19</v>
       </c>
       <c r="M4" t="s" s="6">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N4" t="s" s="6">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C5" s="9" t="n">
         <v>310.0</v>
@@ -1697,10 +1712,10 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C6" s="9" t="n">
         <v>310.0</v>
@@ -1741,22 +1756,22 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="3">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13">
@@ -1781,16 +1796,16 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C14" s="8" t="n">
         <v>45930.0</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E14" s="9" t="n">
         <v>560.0</v>
@@ -1801,16 +1816,16 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C15" s="8" t="n">
         <v>45930.0</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E15" s="9" t="n">
         <v>560.0</v>
@@ -1821,16 +1836,16 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C16" s="8" t="n">
         <v>46022.0</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E16" s="9" t="n">
         <v>560.0</v>
@@ -1841,16 +1856,16 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C17" s="8" t="n">
         <v>46022.0</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E17" s="9" t="n">
         <v>560.0</v>
@@ -1861,16 +1876,16 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C18" s="8" t="n">
         <v>46112.0</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E18" s="9" t="n">
         <v>336.0</v>
@@ -1881,16 +1896,16 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C19" s="8" t="n">
         <v>46112.0</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E19" s="9" t="n">
         <v>336.0</v>
@@ -1901,16 +1916,16 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C20" s="8" t="n">
         <v>46188.0</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E20" s="9" t="n">
         <v>383.85</v>
@@ -1921,16 +1936,16 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C21" s="8" t="n">
         <v>46188.0</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E21" s="9" t="n">
         <v>383.85</v>
@@ -1955,28 +1970,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="4">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="5">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B4" t="s" s="5">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6">
@@ -1984,39 +1999,39 @@
         <v>11</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11">
@@ -2024,93 +2039,93 @@
         <v>14</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="3">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
